--- a/Pune-March-2026.xlsx
+++ b/Pune-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="105">
   <si>
     <t>Sr. No</t>
   </si>
@@ -256,22 +256,19 @@
     <t>MH02GH7486</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Invicto</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>INVICTO</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>EC3</t>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>DZIRE</t>
-  </si>
-  <si>
-    <t>DZIRE PETROL</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -1036,7 +1033,7 @@
         <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H5">
         <v>192764</v>
@@ -1116,7 +1113,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H6">
         <v>203051</v>
@@ -1276,7 +1273,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H8">
         <v>128464</v>
@@ -1356,7 +1353,7 @@
         <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H9">
         <v>198816</v>
@@ -1436,7 +1433,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>124124</v>
@@ -1596,7 +1593,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12">
         <v>97010</v>
@@ -1676,7 +1673,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H13">
         <v>52200</v>
@@ -1756,7 +1753,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H14">
         <v>51521</v>
@@ -1836,7 +1833,7 @@
         <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H15">
         <v>100843</v>
@@ -1916,7 +1913,7 @@
         <v>82</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H16">
         <v>31440</v>
@@ -2156,7 +2153,7 @@
         <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H19">
         <v>36900</v>
@@ -2316,7 +2313,7 @@
         <v>83</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21">
         <v>30568</v>
@@ -2716,7 +2713,7 @@
         <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H26">
         <v>85020</v>
@@ -2796,7 +2793,7 @@
         <v>84</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H27">
         <v>81935</v>
@@ -2876,7 +2873,7 @@
         <v>84</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H28">
         <v>65045</v>
@@ -3756,7 +3753,7 @@
         <v>84</v>
       </c>
       <c r="G39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39">
         <v>59994</v>
@@ -3836,7 +3833,7 @@
         <v>84</v>
       </c>
       <c r="G40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H40">
         <v>52710</v>
@@ -3916,7 +3913,7 @@
         <v>84</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H41">
         <v>41891</v>
@@ -4156,7 +4153,7 @@
         <v>84</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H44">
         <v>70468</v>
@@ -4233,10 +4230,10 @@
         <v>71</v>
       </c>
       <c r="F45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H45">
         <v>37550</v>
@@ -4313,10 +4310,10 @@
         <v>72</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H46">
         <v>53403</v>
@@ -4393,10 +4390,10 @@
         <v>73</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H47">
         <v>107742</v>
@@ -4473,10 +4470,10 @@
         <v>74</v>
       </c>
       <c r="F48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H48">
         <v>53845</v>
@@ -4553,10 +4550,10 @@
         <v>75</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H49">
         <v>39810</v>
@@ -4633,10 +4630,10 @@
         <v>76</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H50">
         <v>33301</v>
@@ -4713,10 +4710,10 @@
         <v>77</v>
       </c>
       <c r="F51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H51">
         <v>18365</v>
@@ -4793,10 +4790,10 @@
         <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H52">
         <v>7609</v>
@@ -4814,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="O52">
         <v>653</v>
@@ -4873,10 +4870,10 @@
         <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H53">
         <v>11033</v>
@@ -4894,10 +4891,10 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="O53">
         <v>1390</v>
